--- a/mass-total-services-2025/MassTotalServices_2025_Balance_L_M1_M2.xlsx
+++ b/mass-total-services-2025/MassTotalServices_2025_Balance_L_M1_M2.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule L" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule M-1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule M-2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conciliacao" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conciliacao" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule L" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule M-1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule M-2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base do Socio" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -87,9 +88,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -98,12 +101,15 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,10 +475,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="130" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -482,126 +488,150 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Notas e pontos para confirmar com o cliente</t>
+          <t>Correcoes aplicadas e pendencias</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MASS TOTAL SERVICES INC  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1. O Schedule L da declaracao preparada NAO fecha com o M-2: inicio tudo zero e Retained Earnings fim (31,610) vs AAA fim 87,412.</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CORRECOES (o que muda na declaracao federal):</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   O worksheet M-2 do software mostra diferenca de 41,308; somando o AAA inicial (77,714) a diferenca real e 119,022.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1. Distribuicoes K 16d e K-1 16D: 220,000 -&gt; 339,022. Retiradas do socio sem nota promissoria/juros = distribuicao (IRC 1368).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2. Correcao proposta: Retained earnings inicio = 77,714 (lucro 2024 78,491 - 777 nao dedutivel, sem distribuicoes em 2024)</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2. Schedule M-2: linha 7 = 307,412 (limitada ao AAA) e linha 8 = 0. O excesso de 31,610 nao entra no M-2.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   e Retained earnings fim = 87,412 = AAA, sem diferenca no worksheet M-2.</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>3. Schedule L inicio: estava zerado; deve ser o saldo final de 2024 (caixa e lucros acumulados 77,714).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3. Caixa inicio 77,714 e SUPOSICAO. Pegar o extrato de 31/12/2024. Se for diferente, a diferenca entra como</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>4. Schedule L fim: Retained earnings (31,610) (igual ao original). O 39,519 sai de Accounts payable (L16) e vai para notes payable (L20).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Loan to shareholder no inicio (ex.: extrato 20,000 -&gt; L7 inicio 57,714) - basta mudar Dados!B15.</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>5. Socio: distribuicao excede a base em 31,610 = ganho de capital de longo prazo no 1040 (Form 8949/Sch D). Form 7203 obrigatorio.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4. As saidas de caixa nao explicadas (119,022) estao como Loans to shareholders (L7).</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>6. Form 4562: o BMW estava na Part II (nao listado). Carro e listed property -&gt; Part V, com % de uso e milhas (Section B).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Se o cliente confirmar que foi retirada pessoal, o certo e aumentar as distribuicoes (K16d / M-2 L7) para 339,022.</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>7. K-1: o nome do socio esta 'ERLI MARQUES DE MORAIS PRESIDENT' - remover 'PRESIDENT' do campo de nome.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Nesse caso a distribuicao passa do AAA (307,412) e pode gerar ganho de capital para o acionista se exceder a base.</t>
-        </is>
-      </c>
+      <c r="A13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Emprestimo ao acionista precisa de nota promissoria/juros para o IRS aceitar; caso contrario vira distribuicao.</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PENDENCIAS (mudam os numeros - ajustar na aba Dados):</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5. O 39,519 (= custo do BMW) foi tratado como financiamento do carro (L20), nao contas a pagar (L16).</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>a. Modelo do BMW: se for carro de passeio ate 6,000 lbs, a depreciacao fica limitada a 20,200 (IRC 280F). Mudar Dados!B13 para 1.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Confirmar saldo do financiamento em 31/12/2025 e se houve juros pagos (deduziveis, L13 - hoje em branco).</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>b. Log de milhas: uso comercial precisa ser &gt; 50% para ter bonus; % menor reduz a depreciacao (Dados!B12).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>6. Gifts 1,671: presentes de negocio sao dedutiveis so ate $25 por pessoa. O excesso e nao dedutivel:</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>c. Extrato 31/12/2024: se o caixa era menor que 77,714, a diferenca foi retirada em 2024 -&gt; emendar K-1 2024 (16D).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   vai para M-1 L3 e M-2 L5 (e K16c). Basta colocar o valor em Dados!B18 - tudo recalcula.</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>d. Contrato do financiamento: saldo em 31/12/2025 e juros pagos (dedutiveis na linha 13).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>7. Schedule B Q11: receita &gt; 250,000, entao L e M-1 sao obrigatorios em 2025.</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>e. Capital aportado pelo socio na abertura (2023): aumenta a base e reduz o ganho de capital (Dados!B21).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>8. Compensation of officers (L7) esta zero com lucro de 229,698 - IRS espera salario razoavel para acionista ativo (risco).</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>f. Gifts 1,671: so $25 por pessoa por ano e dedutivel (IRC 274(b)); excesso em Dados!B20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>g. Salario do socio: S corp com socio que trabalha precisa pagar salario razoavel via payroll (W-2). Iniciar em 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>h. 1099: Schedule B Q14 em branco - se pagou terceirizados &gt;= $600 (incluido nas compras de 128,185), emitir 1099-NEC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>i. Prazo: 1120-S com extensao vencia 15/09/2026. Se ainda nao foi transmitida, transmitir ja; multa $255/socio/mes (pedir First-Time Abatement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>j. Massachusetts: o balanco final e o mesmo ja declarado no Schedule A (caixa 7,909, passivo 39,519, capital -31,610).</t>
         </is>
       </c>
     </row>
@@ -616,12 +646,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
@@ -629,31 +659,31 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dados de entrada (azul = numero digitado, tirado da declaracao)</t>
+          <t>Dados de entrada (azul = digitado; amarelo = confirmar com o cliente)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MASS TOTAL SERVICES INC  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Fonte</t>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Fonte / observacao</t>
         </is>
       </c>
     </row>
@@ -663,7 +693,7 @@
           <t>Receita bruta (1120-S L1c)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="6" t="n">
         <v>445989</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -678,7 +708,7 @@
           <t>Custo das mercadorias - compras (1125-A)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="6" t="n">
         <v>128185</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -693,7 +723,7 @@
           <t>Reparos e manutencao (L9)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="6" t="n">
         <v>801</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -708,7 +738,7 @@
           <t>Impostos e licencas (L12)</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="6" t="n">
         <v>4880</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -720,136 +750,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Depreciacao (L14) - BMW, bonus 100%</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>39520</v>
+          <t>Outras despesas (L20)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>42905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Form 4562 / Depr. detail</t>
+          <t>Statement #2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Outras despesas (L20)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>42905</v>
+          <t>BMW - custo (em servico 08/15/2025)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>39520</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Statement #2</t>
+          <t>Depreciation detail</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Distribuicoes ao acionista (K 16d)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>220000</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Wks DIST</t>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>BMW - % uso comercial</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMAR com log de milhas (Form 4562 Part V)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AAA inicio do ano (M-2 L1)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>77714</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>M-2 / 2024: 78,491 - 777 nao dedutivel</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>BMW e carro de passeio ate 6,000 lbs GVWR? (1=sim, 0=nao)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMAR modelo. 1 = aplica limite IRC 280F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Caixa 31/12/2025 (extrato)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>7909</v>
+          <t>Limite 280F 1o ano com bonus (Rev. Proc. 2025-16)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>20200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sch L / MA Sch A L16</t>
+          <t>carros em servico em 2025</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Caixa 31/12/2024 (extrato)</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Distribuicoes registradas (Wks DIST)</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>77714</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>SUPOSICAO - confirmar extrato de 12/2024</t>
+        <v>220000</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>K 16d original</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BMW - custo (comprado 08/15/2025)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>39520</v>
+          <t>AAA inicio do ano (M-2 L1)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>77714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Depr. detail</t>
+          <t>2024: 78,491 - 777 nao dedutivel</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Financiamento BMW / contas a pagar 31/12/2025</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
+          <t>Caixa 31/12/2025 (extrato)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>7909</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sch L / MA Sch A L16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Caixa 31/12/2024 (extrato)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>77714</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMAR extrato de 12/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Saldo financiamento BMW 31/12/2025</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
         <v>39519</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sch L L16 / MA Sch A L21</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Despesas nao dedutiveis 2025 (K 16c)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMAR contrato (estava como accounts payable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Despesas nao dedutiveis 2025 (ex.: presentes acima de $25/pessoa)</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>nenhuma na declaracao</t>
-        </is>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMAR lista de presentes (gifts 1,671)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Base do sócio - capital aportado na abertura (2023)</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMAR - aumenta a base e reduz o ganho</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Depreciacao calculada (federal)</t>
+        </is>
+      </c>
+      <c r="B23" s="10">
+        <f>IF(Dados!$B$13=1,MIN(Dados!$B$11*Dados!$B$12,Dados!$B$14),Dados!$B$11*Dados!$B$12)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -858,6 +944,163 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Demonstracao de Resultado 2025 (Income Statement per books)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Conta</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Receita bruta (Gross receipts)</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>Dados!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>(-) Custo das mercadorias vendidas (COGS)</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>-Dados!$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Lucro bruto (Gross profit)</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>B6+B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>(-) Reparos e manutencao</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>-Dados!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>(-) Impostos e licencas</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>-Dados!$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>(-) Depreciacao (BMW)</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>-Dados!$B$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>(-) Outras despesas</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>-Dados!$B$10+Dados!$B$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>(-) Despesas nao dedutiveis</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>-Dados!$B$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Lucro liquido contabil (Net income per books)</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>SUM(B8:B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Lucro fiscal - 1120-S L22 (lucro contabil + nao dedutiveis)</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B14+Dados!$B$20</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -876,136 +1119,143 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Demonstracao de Resultado 2025 (Income Statement per books)</t>
+          <t>Conciliacao de caixa - retiradas do socio nao registradas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MASS TOTAL SERVICES INC  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Saida de caixa sem despesa documentada = distribuicao ao socio (IRC 1368)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Conta</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Movimento</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Receita bruta (Gross receipts)</t>
-        </is>
-      </c>
-      <c r="B6" s="8">
-        <f>Dados!$B$6</f>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Caixa inicio (31/12/2024)</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>Dados!$B$18</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>(-) Custo das mercadorias vendidas (COGS)</t>
-        </is>
-      </c>
-      <c r="B7" s="8">
-        <f>-Dados!$B$7</f>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>(+) Lucro liquido contabil</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>DRE!B14</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Lucro bruto (Gross profit)</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
-        <f>B6+B7</f>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>(+) Depreciacao (nao e saida de caixa)</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>Dados!$B$23</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>(-) Reparos e manutencao</t>
-        </is>
-      </c>
-      <c r="B9" s="8">
-        <f>-Dados!$B$8</f>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>(-) Compra BMW</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>-Dados!$B$11</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>(-) Impostos e licencas</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>-Dados!$B$9</f>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>(+) Financiamento BMW</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>Dados!$B$19</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>(-) Depreciacao</t>
-        </is>
-      </c>
-      <c r="B11" s="8">
-        <f>-Dados!$B$10</f>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>(-) Distribuicoes registradas</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>-Dados!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>(-) Outras despesas (seguro, telefone, correio, etc.)</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>-Dados!$B$11</f>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Caixa que deveria existir em 31/12/2025</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>SUM(B6:B11)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>(-) Despesas nao dedutiveis</t>
-        </is>
-      </c>
-      <c r="B13" s="8">
-        <f>-Dados!$B$18</f>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Caixa real em 31/12/2025 (extrato)</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>Dados!$B$17</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Lucro liquido contabil (Net income per books)</t>
-        </is>
-      </c>
-      <c r="B14" s="10">
-        <f>SUM(B8:B13)</f>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Retiradas nao registradas (distribuicao adicional)</t>
+        </is>
+      </c>
+      <c r="B14" s="15">
+        <f>B12-B13</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Confere com 1120-S L22 (229,698)?</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>IF(B14+Dados!$B$18=229698,"OK","VERIFICAR")</f>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL DE DISTRIBUICOES 2025 (K 16d / K-1 16D)</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>Dados!$B$15+B14</f>
         <v/>
       </c>
     </row>
@@ -1014,13 +1264,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1033,222 +1283,188 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Schedule L - Balance Sheets per Books (corrigido)</t>
+          <t>Schedule L - Balance Sheets per Books (correto)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MASS TOTAL SERVICES INC  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Colunas (a)/(c) = bruto; (b)/(d) = liquido, como no formulario</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Linha</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>(a) Inicio bruto</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>(b) Inicio</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>(c) Fim bruto</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>(d) Fim</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>ATIVO (Assets)</t>
-        </is>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1  Cash</t>
+        </is>
+      </c>
+      <c r="C6" s="11">
+        <f>Dados!$B$18</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
+        <f>Dados!$B$17</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>1  Cash</t>
-        </is>
-      </c>
-      <c r="C7" s="8">
-        <f>Dados!$B$15</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>Dados!$B$14</f>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>10a Buildings and other depreciable assets (BMW)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
+        <f>Dados!$B$11</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>7  Loans to shareholders</t>
-        </is>
-      </c>
-      <c r="C8" s="8">
-        <f>Dados!$B$13-Dados!$B$15</f>
-        <v/>
-      </c>
-      <c r="E8" s="8">
-        <f>C8+Conciliacao!B16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>10a Buildings and other depreciable assets (BMW)</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>10b Less accumulated depreciation  (liquido em b/d)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="8">
-        <f>Dados!$B$16</f>
+      <c r="C8" s="11">
+        <f>B7+B8</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>-Dados!$B$23</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>D7+D8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>10b Less accumulated depreciation</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>15 Total assets</t>
+        </is>
+      </c>
+      <c r="C10" s="12">
+        <f>C6+C8</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>E6+E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>20 Mortgages, notes, bonds payable &gt;= 1 yr (financ. BMW)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="8">
-        <f>-Dados!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Liquido imobilizado</t>
-        </is>
-      </c>
-      <c r="C11" s="8">
-        <f>B9+B10</f>
-        <v/>
-      </c>
-      <c r="E11" s="8">
-        <f>D9+D10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>15 Total assets</t>
-        </is>
-      </c>
-      <c r="C12" s="10">
-        <f>C7+C8+C11</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>E7+E8+E11</f>
+      <c r="E12" s="11">
+        <f>Dados!$B$19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>22 Capital stock</t>
+        </is>
+      </c>
+      <c r="C13" s="11">
+        <f>Dados!$B$21</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>Dados!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>PASSIVO E PATRIMONIO (Liabilities &amp; Equity)</t>
-        </is>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>24 Retained earnings</t>
+        </is>
+      </c>
+      <c r="C14" s="11">
+        <f>Dados!$B$18-Dados!$B$21</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>C14+DRE!B14-Conciliacao!$B$16</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>20 Mortgages, notes, bonds payable &gt;= 1 yr (financ. BMW)</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
-        <f>Dados!$B$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>22 Capital stock</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0</v>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>27 Total liabilities and shareholders' equity</t>
+        </is>
+      </c>
+      <c r="C15" s="12">
+        <f>SUM(C12:C14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>SUM(E12:E14)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>24 Retained earnings</t>
-        </is>
-      </c>
-      <c r="C17" s="8">
-        <f>Dados!$B$13</f>
-        <v/>
-      </c>
-      <c r="E17" s="8">
-        <f>'Schedule M-2'!B13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>27 Total liabilities and shareholders' equity</t>
-        </is>
-      </c>
-      <c r="C18" s="10">
-        <f>SUM(C15:C17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>SUM(E15:E17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Diferenca (tem que ser zero)</t>
         </is>
       </c>
-      <c r="C20" s="8">
-        <f>C12-C18</f>
-        <v/>
-      </c>
-      <c r="E20" s="8">
-        <f>E12-E18</f>
+      <c r="C17" s="11">
+        <f>C10-C15</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
+        <f>E10-E15</f>
         <v/>
       </c>
     </row>
@@ -1257,7 +1473,326 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Schedule M-1 - Reconciliation of Income per Books with Income per Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Linha</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1  Net income (loss) per books</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>DRE!B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2  Income on Sch K not recorded on books</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>3  Expenses on books not on Sch K (nao dedutiveis)</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>Dados!$B$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>4  Add lines 1 through 3</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(B6:B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>5  Income on books not on Sch K</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>6  Deductions on Sch K not charged against book income</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7  Add lines 5 and 6</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>B10+B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>8  Income (loss) Schedule K line 18</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>B9-B12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Schedule M-2 - AAA / OAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Linha 7 limitada a linha 6: distribuicao nao deixa o AAA negativo (Reg. 1.1368-2(a)(3)(iii))</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Linha</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>(a) AAA</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>(d) OAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1  Balance at beginning of tax year</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>Dados!$B$16</f>
+        <v/>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2  Ordinary income from page 1, line 22</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>'Schedule M-1'!B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>3  Other additions</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>4  Loss from page 1, line 22</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>5  Other reductions (nao dedutiveis)</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>-Dados!$B$20</f>
+        <v/>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>6  Combine lines 1 through 5</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>SUM(B6:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="12">
+        <f>SUM(C6:C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>7  Distributions (limitado ao AAA)</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>MAX(0,MIN(B11,Conciliacao!$B$16))</f>
+        <v/>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>8  Balance at end of tax year</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>B11-B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>C11-C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Distribuicao acima do AAA (nao entra no M-2)</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>Conciliacao!$B$16-B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Conferencia: RE fim (Sch L) = AAA fim - excesso?</t>
+        </is>
+      </c>
+      <c r="B16" s="11">
+        <f>IF('Schedule L'!E14=B13+C13-B15,"OK","VERIFICAR")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1276,455 +1811,143 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Schedule M-1 - Reconciliation of Income per Books with Income per Return</t>
+          <t>Base das acoes do socio (Form 7203) - Erli Marques de Morais, 100%</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MASS TOTAL SERVICES INC  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Ordem: aumentos -&gt; distribuicoes -&gt; nao dedutiveis -&gt; perdas (IRC 1368(d), Reg. 1.1367-1(f))</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Linha</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>1  Net income (loss) per books</t>
-        </is>
-      </c>
-      <c r="B6" s="8">
-        <f>DRE!B14</f>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Capital aportado na abertura</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>Dados!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2  Income on Sch K not recorded on books</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>(+) Lucro 2024 menos nao dedutiveis 2024</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>Dados!$B$16</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>3  Expenses on books not on Sch K (3a depr / 3b T&amp;E)</t>
-        </is>
-      </c>
-      <c r="B8" s="8">
-        <f>Dados!$B$18</f>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Base no inicio de 2025</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>B6+B7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>4  Add lines 1 through 3</t>
-        </is>
-      </c>
-      <c r="B9" s="10">
-        <f>SUM(B6:B8)</f>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>(+) Lucro ordinario 2025 (K-1 box 1)</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>'Schedule M-1'!B13</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>5  Income on books not on Sch K (tax-exempt interest)</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Base antes das distribuicoes</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>B8+B9</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>6  Deductions on Sch K not charged against book income</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>0</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>(-) Distribuicoes 2025 (K-1 box 16D)</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>-Conciliacao!$B$16</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>7  Add lines 5 and 6</t>
-        </is>
-      </c>
-      <c r="B12" s="10">
-        <f>B10+B11</f>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Distribuicao isenta (ate a base)</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>MIN(B10,Conciliacao!$B$16)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>8  Income (loss) Schedule K line 18 (line 4 - line 7)</t>
-        </is>
-      </c>
-      <c r="B13" s="10">
-        <f>B9-B12</f>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>GANHO DE CAPITAL LONGO PRAZO DO SOCIO (excesso sobre a base)</t>
+        </is>
+      </c>
+      <c r="B13" s="15">
+        <f>MAX(0,Conciliacao!$B$16-B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>(-) Nao dedutiveis 2025</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>-Dados!$B$20</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Confere com Schedule K L18 (229,698)?</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>IF(B13=229698,"OK","VERIFICAR")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Schedule M-2 - Analysis of AAA / OAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MASS TOTAL SERVICES INC  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Linha</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>(a) AAA</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>(d) OAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>1  Balance at beginning of tax year</t>
-        </is>
-      </c>
-      <c r="B6" s="8">
-        <f>Dados!$B$13</f>
-        <v/>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>2  Ordinary income from page 1, line 22</t>
-        </is>
-      </c>
-      <c r="B7" s="8">
-        <f>'Schedule M-1'!B13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>3  Other additions</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>4  Loss from page 1, line 22</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>5  Other reductions (nao dedutiveis)</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>-Dados!$B$18</f>
-        <v/>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>6  Combine lines 1 through 5</t>
-        </is>
-      </c>
-      <c r="B11" s="10">
-        <f>SUM(B6:B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="10">
-        <f>SUM(C6:C10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>7  Distributions</t>
-        </is>
-      </c>
-      <c r="B12" s="8">
-        <f>Dados!$B$12</f>
-        <v/>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>8  Balance at end of tax year (line 6 - line 7)</t>
-        </is>
-      </c>
-      <c r="B13" s="10">
-        <f>B11-B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="10">
-        <f>C11-C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Retained earnings (Sch L L24 fim) = AAA + OAA?</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>IF('Schedule L'!E17=B13+C13,"OK","VERIFICAR")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Conciliacao de caixa - de onde sai o Loan to shareholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MASS TOTAL SERVICES INC  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>O dinheiro que saiu do banco e nao esta explicado por despesa/distribuicao registrada</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Movimento</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Caixa inicio (31/12/2024)</t>
-        </is>
-      </c>
-      <c r="B6" s="8">
-        <f>Dados!$B$15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>(+) Lucro liquido contabil</t>
-        </is>
-      </c>
-      <c r="B7" s="8">
-        <f>DRE!B14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>(+) Depreciacao (nao e saida de caixa)</t>
-        </is>
-      </c>
-      <c r="B8" s="8">
-        <f>Dados!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>(-) Compra BMW</t>
-        </is>
-      </c>
-      <c r="B9" s="8">
-        <f>-Dados!$B$16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>(+) Financiamento BMW</t>
-        </is>
-      </c>
-      <c r="B10" s="8">
-        <f>Dados!$B$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>(-) Distribuicoes registradas</t>
-        </is>
-      </c>
-      <c r="B11" s="8">
-        <f>-Dados!$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Caixa que deveria existir em 31/12/2025</t>
-        </is>
-      </c>
-      <c r="B12" s="10">
-        <f>SUM(B6:B11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Caixa real em 31/12/2025 (extrato)</t>
-        </is>
-      </c>
-      <c r="B13" s="8">
-        <f>Dados!$B$14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Saidas nao explicadas</t>
-        </is>
-      </c>
-      <c r="B15" s="10">
-        <f>B12-B13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>-&gt; lancado como Loan to shareholder (Sch L L7)</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>B15</f>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Base no fim de 2025</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>MAX(0,B10-Conciliacao!$B$16-Dados!$B$20)</f>
         <v/>
       </c>
     </row>

--- a/mass-total-services-2025/MassTotalServices_2025_Balance_L_M1_M2.xlsx
+++ b/mass-total-services-2025/MassTotalServices_2025_Balance_L_M1_M2.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -495,143 +495,125 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CORRECOES (o que muda na declaracao federal):</t>
+          <t>DECLARACAO RETIFICADORA (1120-S 2025, EIN 93-3675961) - o que muda:</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>1. Distribuicoes K 16d e K-1 16D: 220,000 -&gt; 339,022. Retiradas do socio sem nota promissoria/juros = distribuicao (IRC 1368).</t>
+          <t>1. Pagina 1, item F (Total assets): 7,909 -&gt; 126,931.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2. Schedule M-2: linha 7 = 307,412 (limitada ao AAA) e linha 8 = 0. O excesso de 31,610 nao entra no M-2.</t>
+          <t>2. Schedule L inicio: caixa 77,714 e retained earnings 77,714 (estava tudo zero).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>3. Schedule L inicio: estava zerado; deve ser o saldo final de 2024 (caixa e lucros acumulados 77,714).</t>
+          <t>3. Schedule L fim: Loans to shareholders (L7) 119,022; financiamento do BMW sai da L16 e vai para a L20; retained earnings 87,412.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>4. Schedule L fim: Retained earnings (31,610) (igual ao original). O 39,519 sai de Accounts payable (L16) e vai para notes payable (L20).</t>
+          <t>4. Schedule M-1, M-2, Schedule K e K-1: sem alteracao (distribuicoes 220,000; AAA final 87,412).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>5. Socio: distribuicao excede a base em 31,610 = ganho de capital de longo prazo no 1040 (Form 8949/Sch D). Form 7203 obrigatorio.</t>
+          <t>5. Form 4562: BMW na Part V (listed property). K-1: tirar 'PRESIDENT' do nome do socio.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6. Form 4562: o BMW estava na Part II (nao listado). Carro e listed property -&gt; Part V, com % de uso e milhas (Section B).</t>
+          <t>6. Massachusetts: Schedules A, B e D com os novos saldos; excise continua 456.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>7. K-1: o nome do socio esta 'ERLI MARQUES DE MORAIS PRESIDENT' - remover 'PRESIDENT' do campo de nome.</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PARA O EMPRESTIMO AO SOCIO SER ACEITO PELO IRS:</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>PENDENCIAS (mudam os numeros - ajustar na aba Dados):</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>a. Nota promissoria assinada (valor 119,022, juros pela taxa AFR do IRS, prazo de pagamento).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>a. Modelo do BMW: se for carro de passeio ate 6,000 lbs, a depreciacao fica limitada a 20,200 (IRC 280F). Mudar Dados!B13 para 1.</t>
+          <t>b. Cobrar juros pela AFR - sem juros, o IRS imputa juros (IRC 7872).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>b. Log de milhas: uso comercial precisa ser &gt; 50% para ter bonus; % menor reduz a depreciacao (Dados!B12).</t>
+          <t>c. O socio precisa devolver de fato (pagamentos registrados no banco).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>c. Extrato 31/12/2024: se o caixa era menor que 77,714, a diferenca foi retirada em 2024 -&gt; emendar K-1 2024 (16D).</t>
+          <t>d. Sem isso, o IRS pode tratar os 119,022 como distribuicao (mude Dados!B22 para 0 para ver o efeito).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>d. Contrato do financiamento: saldo em 31/12/2025 e juros pagos (dedutiveis na linha 13).</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>e. Capital aportado pelo socio na abertura (2023): aumenta a base e reduz o ganho de capital (Dados!B21).</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMAR:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>f. Gifts 1,671: so $25 por pessoa por ano e dedutivel (IRC 274(b)); excesso em Dados!B20.</t>
+          <t>e. Extrato de 31/12/2024 (caixa inicial 77,714 reconstruido). Diferenca vai para Loans to shareholders no inicio.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>g. Salario do socio: S corp com socio que trabalha precisa pagar salario razoavel via payroll (W-2). Iniciar em 2026.</t>
+          <t>f. Modelo/GVWR do BMW e log de milhas (Dados!B12 e B13).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>h. 1099: Schedule B Q14 em branco - se pagou terceirizados &gt;= $600 (incluido nas compras de 128,185), emitir 1099-NEC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>i. Prazo: 1120-S com extensao vencia 15/09/2026. Se ainda nao foi transmitida, transmitir ja; multa $255/socio/mes (pedir First-Time Abatement).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>j. Massachusetts: o balanco final e o mesmo ja declarado no Schedule A (caixa 7,909, passivo 39,519, capital -31,610).</t>
+          <t>g. Contrato do financiamento: saldo em 31/12/2025 e juros pagos.</t>
         </is>
       </c>
     </row>
@@ -646,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -666,7 +648,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
@@ -927,13 +909,28 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Retiradas do socio sem registro: 1 = emprestimo ao socio, 0 = distribuicao</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Distribuicoes de 2025 foram so 220,000 -&gt; emprestimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Depreciacao calculada (federal)</t>
         </is>
       </c>
-      <c r="B23" s="10">
+      <c r="B24" s="10">
         <f>IF(Dados!$B$13=1,MIN(Dados!$B$11*Dados!$B$12,Dados!$B$14),Dados!$B$11*Dados!$B$12)</f>
         <v/>
       </c>
@@ -969,7 +966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1044,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>-Dados!$B$23</f>
+        <f>-Dados!$B$24</f>
         <v/>
       </c>
     </row>
@@ -1106,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1126,7 +1123,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1175,7 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>Dados!$B$23</f>
+        <f>Dados!$B$24</f>
         <v/>
       </c>
     </row>
@@ -1240,7 +1237,7 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Retiradas nao registradas (distribuicao adicional)</t>
+          <t>Retiradas do socio nao registradas</t>
         </is>
       </c>
       <c r="B14" s="15">
@@ -1255,7 +1252,18 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>Dados!$B$15+B14</f>
+        <f>Dados!$B$15+IF(Dados!$B$22=1,0,B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Emprestimo ao socio (Sch L linha 7)</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>IF(Dados!$B$22=1,B14,0)</f>
         <v/>
       </c>
     </row>
@@ -1290,7 +1298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
@@ -1346,36 +1354,50 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>10a Buildings and other depreciable assets (BMW)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
+          <t>7  Loans to shareholders</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="11">
-        <f>Dados!$B$11</f>
+      <c r="E7" s="11">
+        <f>Conciliacao!B17</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>10b Less accumulated depreciation  (liquido em b/d)</t>
+          <t>10a Buildings and other depreciable assets (BMW)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="11">
-        <f>B7+B8</f>
-        <v/>
-      </c>
       <c r="D8" s="11">
-        <f>-Dados!$B$23</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
-        <f>D7+D8</f>
+        <f>Dados!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>10b Less accumulated depreciation  (liquido em b/d)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="11">
+        <f>B8+B9</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>-Dados!$B$24</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>D8+D9</f>
         <v/>
       </c>
     </row>
@@ -1386,11 +1408,11 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>C6+C8</f>
+        <f>C6+C7+C9</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>E6+E8</f>
+        <f>E6+E7+E9</f>
         <v/>
       </c>
     </row>
@@ -1499,7 +1521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1653,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1840,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mass Total Services Inc  -  EIN 93-3675960  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
+          <t>Mass Total Services Inc  -  EIN 93-3675961  -  Form 1120-S 2025 (ano-calendario, regime de caixa)</t>
         </is>
       </c>
     </row>
